--- a/resultados/alvoradadosul/inventario_links.xlsx
+++ b/resultados/alvoradadosul/inventario_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I446"/>
+  <dimension ref="A1:I460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18117,6 +18117,496 @@
         </is>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU4yWT1PVE09T1RjPQ==&amp;ano=2026&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>4</v>
+      </c>
+      <c r="H447" t="n">
+        <v>200</v>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU56ST1ZVEk9WVRjPQ==&amp;ano=2026&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>4</v>
+      </c>
+      <c r="H448" t="n">
+        <v>200</v>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU4yWT1PVE09T1RjPQ==&amp;ano=2025&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>4</v>
+      </c>
+      <c r="H449" t="n">
+        <v>200</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU56ST1ZVEk9WVRjPQ==&amp;ano=2025&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>4</v>
+      </c>
+      <c r="H450" t="n">
+        <v>200</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU4yWT1PVE09T1RjPQ==&amp;ano=2024&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>4</v>
+      </c>
+      <c r="H451" t="n">
+        <v>200</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU56ST1ZVEk9WVRjPQ==&amp;ano=2024&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>4</v>
+      </c>
+      <c r="H452" t="n">
+        <v>200</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU4yWT1PVE09T1RjPQ==&amp;ano=2023&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>4</v>
+      </c>
+      <c r="H453" t="n">
+        <v>200</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU56ST1ZVEk9WVRjPQ==&amp;ano=2023&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>4</v>
+      </c>
+      <c r="H454" t="n">
+        <v>200</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU4yWT1PVE09T1RjPQ==&amp;ano=2022&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>4</v>
+      </c>
+      <c r="H455" t="n">
+        <v>200</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU56ST1ZVEk9WVRjPQ==&amp;ano=2022&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>4</v>
+      </c>
+      <c r="H456" t="n">
+        <v>200</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU4yWT1PVE09T1RjPQ==&amp;ano=2021&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>4</v>
+      </c>
+      <c r="H457" t="n">
+        <v>200</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU56ST1ZVEk9WVRjPQ==&amp;ano=2021&amp;getAjax=1&amp;wad=1</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>4</v>
+      </c>
+      <c r="H458" t="n">
+        <v>200</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU4yWT1PVE09T1RjPQ==&amp;ano=2022&amp;getAjax=1&amp;fisico=3</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>4</v>
+      </c>
+      <c r="H459" t="n">
+        <v>200</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>alvoradadosul</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://www.alvoradadosul.pr.gov.br/ouvidoria/indexAjax.php?pag=TnpNPU9EZz1PR1k9T0RZPU9Uaz1PVFk9T1RrPU9UST1PVGc9TnpBPU9XVT1PVFk9T1RBPU56ST1ZVEk9WVRjPQ==&amp;ano=2022&amp;getAjax=1&amp;fisico=3</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>www.alvoradadosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>4</v>
+      </c>
+      <c r="H460" t="n">
+        <v>200</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:48:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
